--- a/www/download/COUNTRY.NLD.zdW13.xlsx
+++ b/www/download/COUNTRY.NLD.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Países Baixos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.727939807997103</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.764759852979333</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.884290610900269</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.89893298342352</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.938262380158969</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.08271977415814</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.11656987220386</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.05752964058676</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.884017009417596</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803923183139281</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.803793923183733</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.796431999730865</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.729660724026465</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074187573</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948694066692</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.155</t>
+          <t>-0.399955374550369</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.315</t>
+          <t>-0.356400026444354</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.541</t>
+          <t>-0.052521867989316</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7.738</t>
+          <t>-0.235790186151698</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.937</t>
+          <t>-0.274235655246023</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.115</t>
+          <t>-0.261994115744007</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8.282</t>
+          <t>-0.342561435381653</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.324</t>
+          <t>-0.413517303321499</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8.283</t>
+          <t>-0.355621767250763</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8.211</t>
+          <t>-0.380984731479343</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8.252</t>
+          <t>-0.363761623114895</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>8.392</t>
+          <t>-0.36712412106086</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>8.607</t>
+          <t>-0.34203495244387</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>8.738</t>
+          <t>-0.403578533237469</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>8.694</t>
+          <t>-0.382034252074961</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.014</t>
+          <t>-0.181469360874333</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>-0.142125230671583</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.354</t>
+          <t>0.298246897277495</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.565</t>
+          <t>0.0544205703705907</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>0.0193649607181758</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.988</t>
+          <t>0.0513554615807916</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7.152</t>
+          <t>-0.0545414561364813</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>-0.147397425653982</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7.167</t>
+          <t>-0.083218050717524</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.083</t>
+          <t>-0.0966806795692945</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7.105</t>
+          <t>-0.0603545019214039</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>7.227</t>
+          <t>-0.0659497846649715</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.425</t>
+          <t>-0.0798644025986984</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>-0.133713183943075</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>7.473</t>
+          <t>-0.100323136825815</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10445.244</t>
+          <t>-0.0255039446512572</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10702.777</t>
+          <t>0.0406544200004442</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10961.388</t>
+          <t>0.578378761957674</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11146.709</t>
+          <t>0.304674410428773</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11403.058</t>
+          <t>0.260506304032032</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11641.135</t>
+          <t>0.316849026218328</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11791.079</t>
+          <t>0.184091273363136</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11723.033</t>
+          <t>0.0848229259076181</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11603.664</t>
+          <t>-0.0685654327924645</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>11489.169</t>
+          <t>0.145364701749395</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>11496.405</t>
+          <t>0.18764933210623</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>11679.322</t>
+          <t>0.180347546695066</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>11950.122</t>
+          <t>0.170037159754293</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12164.649</t>
+          <t>0.0647927549681964</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12042.709</t>
+          <t>0.104405020451433</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8502.439</t>
+          <t>18416421178.5935</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8679.178</t>
+          <t>18876013210.4052</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8931.979</t>
+          <t>17299033391.6668</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9176.159</t>
+          <t>19300288717.7136</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9443.354</t>
+          <t>20477999918.8423</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9648.194</t>
+          <t>20437578511.2837</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9833.376</t>
+          <t>21293575911.1572</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9812.115</t>
+          <t>18040662240.3964</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9726.175</t>
+          <t>21973053352.4682</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9580.306</t>
+          <t>22099863625.4223</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9554.199</t>
+          <t>22998126311.1988</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9704.286</t>
+          <t>23117404536.888</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9945.624</t>
+          <t>24208397393.3129</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>10062.514</t>
+          <t>26924306780.3156</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9905.508</t>
+          <t>23516705805.3819</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>10651923032.5477</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>10324478089.5758</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>7125509346.90427</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>9010272226.51336</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>9826181027.26621</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>9524745923.09501</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>10810766721.816</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>12099807162.0328</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>11818489715.8619</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>11476528779.2115</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>11123524215.8505</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>11371607896.2685</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>11589637136.6886</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>12754956594.7117</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>12129307647.481</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>877185.313693907</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>909124.801409113</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>920045.859381407</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>990256.998498152</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>1048336.4201723</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>1096086.56388698</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>1098540.798173</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>931613.891412521</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>875035.847069893</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>787692.439210284</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>766121.7772239</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>42.73</t>
+          <t>718858.092154892</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>636346.018437718</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>604432.561027847</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>614827.790500254</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>41583.6299211919</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>42335.8913035481</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>43148.1441974556</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>42792.9343200526</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>45419.4989098958</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>47220.5162306251</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>46403.0088983629</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>47590.4264959408</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>50749.5254516573</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>55043.2454854175</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>58584.787021751</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>61520.6941269953</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70072.3597817549</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>24.86</t>
+          <t>78418.5257341</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>72581.505702656</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>158684.514485839</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>163808.747090459</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>149641.857519772</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>165269.139876151</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>182397.063447998</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>185047.260170433</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>187241.265487066</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>162100.225922104</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>211656.050698485</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>234146.853353858</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>260978.306859287</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>273864.626027861</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>323136.83738468</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>393464.899605168</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>320367.100921705</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.73</t>
+          <t>-0.201793083948792</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>-0.159359139533918</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>0.253521448859265</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.73</t>
+          <t>0.0184108780231036</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>-0.0389599047380286</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>0.0129607754227443</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>-0.0904089651517177</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>-0.189068491207959</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>-0.177037433307046</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>-0.16522613358896</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>-0.141081697886203</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>-0.146621432384742</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>-0.141851987797291</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>-0.211089875196281</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>-0.183341053761038</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>30.31</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.727939807997103</t>
+          <t>1771.1715361013</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.764759852979333</t>
+          <t>1678.67211048542</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.884290610900269</t>
+          <t>1121.36404569051</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89893298342352</t>
+          <t>1372.46641770787</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262380158969</t>
+          <t>1442.88054902843</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977415814</t>
+          <t>1362.98025737975</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987220386</t>
+          <t>1511.57760062618</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964058676</t>
+          <t>1680.77155061742</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017009417596</t>
+          <t>1648.90790758824</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923183139281</t>
+          <t>1620.21132918429</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923183733</t>
+          <t>1565.53791994536</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999730865</t>
+          <t>1573.42299740616</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660724026465</t>
+          <t>1560.95801062381</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074187573</t>
+          <t>1689.30402618763</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948694066692</t>
+          <t>1623.17795535363</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>15378245345.4754</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>14851789971.228</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>11201938266.1422</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>13378049683.2371</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>14144082277.0805</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>14216991443.4561</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>15923985249.7145</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>16954015950.7959</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>18223758713.9256</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>19128747427.858</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>19706037509.9574</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>19214558246.7323</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>20147750126.8183</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>21741402517.456</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>18832501492.8033</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>16977118503.7862</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>16456328944.5182</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>12581642127.307</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>14983579245.1125</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>15728374404.6279</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>15741113713.8509</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>17197679346.4175</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>18343317303.3582</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>19909294337.2751</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>20669493196.5598</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>20930485784.9008</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>20572552700.4028</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>21215440508.3569</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>22726568685.6818</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>19914814270.0131</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>-1598873158.31074</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>-1604538973.29016</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>-1379703861.16476</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>-1605529561.87542</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>-1584292127.54735</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>-1524122270.39475</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>-1273694096.70302</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>-1389301352.56227</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.721</t>
+          <t>-1685535623.34953</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.941</t>
+          <t>-1540745768.70179</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.998</t>
+          <t>-1224448274.94341</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>-1357994453.67051</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>-1067690381.53863</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-985166168.225753</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1082312777.20977</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>1413.7613696291</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1411.16036739888</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>1405.65388325266</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>1397.7347295151</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>1386.66606028993</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>1380.64553840129</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>1374.91743400705</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>1362.99060947692</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>1356.98948386912</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>1352.51007566614</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1344.66917209423</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>1342.72546377938</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>1339.53301394872</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1332.70905013111</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1325.58279857741</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>1459.85815229363</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>1463.16357302463</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>1453.49859734535</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1440.47768283466</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>1436.70655570081</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>1434.43485459273</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>1423.63018751925</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>1408.35517829464</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>1400.88011793618</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>1399.18929234626</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>1393.23430767021</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>1391.66321928023</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>1388.48638669799</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1392.22432054302</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>1385.25206281064</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-40</t>
+          <t>218027.084282411</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-35.64</t>
+          <t>217152.718214827</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-5.25</t>
+          <t>206768.148740123</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-23.58</t>
+          <t>207986.069925308</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-27.42</t>
+          <t>212322.094138053</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-26.2</t>
+          <t>214498.067189643</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-34.26</t>
+          <t>210812.087293922</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-41.35</t>
+          <t>222189.914982798</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-35.56</t>
+          <t>266519.660973371</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-38.1</t>
+          <t>313839.379246555</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-36.38</t>
+          <t>341871.736434771</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-36.71</t>
+          <t>374203.809168873</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-34.2</t>
+          <t>436276.695560478</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-40.36</t>
+          <t>527855.087696026</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-38.2</t>
+          <t>431915.949944875</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-18.15</t>
+          <t>8339038067.95146</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-14.21</t>
+          <t>8533476272.98041</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>7885811919.99806</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>8962613125.39874</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>9871030478.18798</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>10204753197.4996</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>10350456527.6247</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-14.74</t>
+          <t>8533135135.22793</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>10833583382.4666</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-9.67</t>
+          <t>11189538495.2091</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>12016408324.8031</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>12236926328.0861</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-7.99</t>
+          <t>12886196847.6763</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-13.37</t>
+          <t>15017595147.4613</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-10.03</t>
+          <t>12786998460.5879</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>183512.62021827</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>184335.763393688</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>174567.50063862</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>178706.421023756</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.05</t>
+          <t>184993.302417061</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>183369.48791768</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>178768.266007625</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>184656.766492686</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>222165.962424287</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>257878.856784458</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18.76</t>
+          <t>276263.221877456</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>309369.256717158</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>357993.67823002</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>6.48</t>
+          <t>438605.723588208</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>362207.699963329</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10445.244</t>
+          <t>18960526691.694</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10702.777</t>
+          <t>19047244438.8481</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10961.388</t>
+          <t>15191218857.3886</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11146.709</t>
+          <t>18582492294.5213</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11403.058</t>
+          <t>20424835712.1921</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11641.135</t>
+          <t>20281058080.7317</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11791.079</t>
+          <t>21783520034.1379</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11723.033</t>
+          <t>20285259191.1236</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11603.664</t>
+          <t>23217109123.8726</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>11489.169</t>
+          <t>23541661741.7808</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11496.405</t>
+          <t>24364323018.7129</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>11679.322</t>
+          <t>24800910674.6424</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>11950.122</t>
+          <t>25926873344.0779</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>12164.649</t>
+          <t>29464360024.7562</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>12042.709</t>
+          <t>25344939566.4172</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8502.439</t>
+          <t>34514.46406414</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8679.178</t>
+          <t>32816.9548211389</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8931.979</t>
+          <t>32200.6481015032</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9176.159</t>
+          <t>29279.6489015525</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9443.354</t>
+          <t>27328.7917209921</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9648.194</t>
+          <t>31128.5792719626</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9833.376</t>
+          <t>32043.8212862972</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9812.115</t>
+          <t>37533.148490112</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>9726.175</t>
+          <t>44353.698549084</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9580.306</t>
+          <t>55960.5224620967</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9554.199</t>
+          <t>65608.5145573149</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9704.286</t>
+          <t>64834.5524517154</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>9945.624</t>
+          <t>78283.0173304588</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>10062.514</t>
+          <t>89249.364107818</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>9905.508</t>
+          <t>69708.2499815464</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18416.421</t>
+          <t>-10621488623.7425</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18876.013</t>
+          <t>-10513768165.8677</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17299.033</t>
+          <t>-7305406937.39052</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>19300.289</t>
+          <t>-9619879169.12261</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>-10553805234.0041</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>20437.579</t>
+          <t>-10076304883.2322</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21293.576</t>
+          <t>-11433063506.5131</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>18040.662</t>
+          <t>-11752124055.8957</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>21973.053</t>
+          <t>-12383525741.406</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>22099.864</t>
+          <t>-12352123246.5718</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>22998.126</t>
+          <t>-12347914693.9098</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>23117.405</t>
+          <t>-12563984346.5563</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>24208.397</t>
+          <t>-13040676496.4015</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>26924.307</t>
+          <t>-14446764877.2948</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>23516.706</t>
+          <t>-12557941105.8293</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>176167.03781</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>170677.10748</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>154661.82466</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>157627.99106</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>156102.38865</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>147529.40157</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>152020.04329</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>167422.26007</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>206325.21695</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>232158.99726</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>242511.16397</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>258749.02057</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>298198.86517</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>339593.02174</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>306192.06371</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4826.064</t>
+          <t>0.0828179861301035</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4878.45</t>
+          <t>0.0828750548787174</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4988.051</t>
+          <t>0.088068106300366</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4997.4</t>
+          <t>0.0885265640213877</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>5099.317</t>
+          <t>0.0894543630946711</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5215.279</t>
+          <t>0.0934616912147827</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5277.074</t>
+          <t>0.0934442956621288</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5296.494</t>
+          <t>0.0931499666111589</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5268.557</t>
+          <t>0.0917243668531614</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5195.236</t>
+          <t>0.0921679516110062</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5162.653</t>
+          <t>0.0985318950757591</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5193.072</t>
+          <t>0.100560990498268</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5249.601</t>
+          <t>0.103204126740359</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5366.081</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>5327.881</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>214079.514468347</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>211595.833904053</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>193626.391223694</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>204747.186797824</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>210329.226889465</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>195621.254394251</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>203650.489479185</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>225832.914828991</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>277994.651057547</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>312256.202294237</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>316701.821837909</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>332639.823540857</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>384163.475688043</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>434081.231334496</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>417675.806562603</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10651.923</t>
+          <t>254812.107116176</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10324.478</t>
+          <t>252872.209196045</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7125.509</t>
+          <t>230613.67452377</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9010.272</t>
+          <t>241436.717045849</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9826.181</t>
+          <t>246776.722249077</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9524.746</t>
+          <t>229293.949001612</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10810.767</t>
+          <t>237472.510775032</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>12099.807</t>
+          <t>262702.819050097</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11818.49</t>
+          <t>323233.238782572</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>11476.529</t>
+          <t>364523.867293859</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>11123.524</t>
+          <t>370710.693728264</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>11371.608</t>
+          <t>389610.62877315</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>11589.637</t>
+          <t>449130.385402166</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>12754.957</t>
+          <t>507293.478975141</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>12129.308</t>
+          <t>488282.846078824</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-20.18</t>
+          <t>1496157.71432994</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>1478277.10103172</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.35</t>
+          <t>1317570.51764548</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1344462.34031398</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>1343875.25775235</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1236786.42357057</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>1268976.89371771</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-18.91</t>
+          <t>1386250.90826854</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-17.7</t>
+          <t>1720549.65296268</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-16.52</t>
+          <t>1941061.64441195</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-14.11</t>
+          <t>1997579.77597407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>2106550.71809876</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-14.19</t>
+          <t>2389477.35353878</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-21.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-18.33</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>254812.107116176</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>263395.628118059</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>271597.527540224</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>283391.754634822</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>296372.924171784</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>307233.977882562</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>313823.072770171</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>313332.213441468</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>315037.119696603</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>322971.516033075</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>323774.00346502</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>334532.029794109</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>350683.5963835</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>367108.493360462</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>371617.068337142</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>214079.514468347</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>220585.102493354</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>228505.739959758</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>240711.598582331</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>252303.567449044</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>261847.057393588</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>269401.940246859</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>269113.367741665</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>270383.886646088</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>275350.60699783</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>275277.742056614</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>285522.614991753</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>299766.400232008</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>313096.873516325</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>315879.92168012</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>123908.768833824</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>122512.295873955</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>116035.94040623</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>119020.631444151</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>120215.505260923</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>115592.150818388</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>118578.652044968</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>129129.225819903</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>157816.327557428</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>178903.675716141</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>196825.320891736</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>211836.82674685</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>246603.923637834</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>271228.928544859</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>222533.708471176</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8502438633.82475</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8679178145.08419</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>8931978800.39168</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>9176159249.43066</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>9443353950.50529</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9648194015.96294</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9833376490</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>9812114878</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>9726174631</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>9580306302</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9554198533</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>9704286458</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>9945624071</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10062514399</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9905507602</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10445244203.6327</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10702776704.0685</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10961388159.0455</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>11146708726.7442</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>11403058040.3236</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>11641134545.9245</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>11791078936</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>11723033019</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>11603663726</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>11489168633</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>11496405247</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>11679322035</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>11950121943</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>12164648567.3088</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>12042709012.2354</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4826064126.32517</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4878450374.07404</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>4988050800.97069</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4997399926.4115</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>5099317266.45304</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5215278555.96398</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5277073886</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5296493607</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5268557297</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5195236243</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5162652590</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5193072191</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5249601208</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5366080802.23595</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5327881394.84444</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7154972</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>7314819</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>7541382</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>7738203</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>7936943</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>8115485</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8282403</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>8323918</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>8283124</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>8211304</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>8251595</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>8392348</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>8606582</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>8737563.61515372</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>8693514.58520918</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6014055</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6150384</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6354323</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6565022</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6810114</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6988176</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7151976</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7198960</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7167465</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7083353</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>7105241</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7227305</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7424695</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7550421</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7472568</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10445244203.6327</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10702776704.0685</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10961388159.0455</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>11146708726.7442</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>11403058040.3236</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>11641134545.9245</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11791078936</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>11723033019</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>11603663726</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>11489168633</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>11496405247</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>11679322035</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>11950121943</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>12164648567.3088</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>12042709012.2354</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>8502438633.82475</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8679178145.08419</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8931978800.39168</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>9176159249.43066</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>9443353950.50529</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9648194015.96294</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9833376490</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>9812114878</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>9726174631</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>9580306302</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>9554198533</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>9704286458</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>9945624071</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>10062514399</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>9905507602</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.20338329807979</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.217718735841253</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.246065370493181</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.239809308186684</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.274745773150394</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.258347640491807</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.250979014873388</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.273633430420754</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.283491993756359</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.330140487056565</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.336217130235099</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.333748231790221</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.319093753171804</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.333741192387393</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.339627936389669</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.472347731883114</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.47653385884818</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.465950798332348</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.466940112032318</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.456406384073613</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.438976928050973</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.443243792582819</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.452809302409808</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.410788258385951</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.426703245660015</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.426587881750408</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.427302669921315</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.441127002744028</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.417658099060937</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.414835106175788</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.324268970037095</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.305747405310566</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.287983831174471</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.293250579780998</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.268847842775994</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.302675431457219</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.305777192543793</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.273557267169439</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.30571974785769</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.243156267283421</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.237194988014493</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.238949098288464</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.239779244084168</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.24860070855167</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.245536957434543</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.155191376679913</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.165497267868503</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.185297732881203</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.181065654202141</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.207357069565396</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.190483692599167</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.182531352602225</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.200458681164414</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.226943761394089</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.245957121096906</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.251300472282877</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.250128342330687</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.248987793745188</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.258089129993417</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.264563599615033</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.467334020449806</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.473177590563234</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.466075156318148</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.467285928622662</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.464069182841793</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.438559146158021</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.443410457536547</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.459312454396778</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.447784685215382</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.445202107804114</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.446375978076828</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.446730278361894</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.453618787929575</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.436687487587405</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.433783964126723</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.377474602870281</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.361325141568263</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.348627110800648</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.351648417175198</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.328573747592811</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.370957161242812</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.374058189861228</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.340228864438809</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.325271553390528</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.308840771098981</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.302323549640295</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.303141379307418</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.297393418325237</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.305223382419178</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.301652436258244</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>786923.58571</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>792352.00521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>734631.79263</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>760876.52075</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>776240.22052</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>743411.19552</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>762957.1837</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>821869.17178</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>997998.89929</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1135221.64746</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1195322.54689</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1281437.71187</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1485992.00088</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1692086.32088</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1521976.41218</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>378720.87595</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>375384.50507</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>346649.61493</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>360457.34849</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>366992.22751</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>344886.09982</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>356051.16282</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>391832.04487</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>481049.56634</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>543427.54301</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>567536.01462</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>601447.45552</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>695734.30904</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>778522.40752</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>710816.55455</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1089112.74824553</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1115849.59196854</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1147329.4202368</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1182375.94917584</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1222559.72367744</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1260041.50260354</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1296393.48653905</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1326227.93547332</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1355541.9207955</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1381600.74956218</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1409754.40131492</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1443364.21253913</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1487985.48051486</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
